--- a/questionnaire_templates/019_personal_reset_and_realignment_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/019_personal_reset_and_realignment_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form1</t>
+          <t>What is your current level of motivation?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,87 +543,87 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>page_1_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>How many hours do you usually spend on social media?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_1_question</t>
+          <t>page_1_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_page_question</t>
+          <t>Have you experienced any recent stress or anxiety?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_option_3</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>select_option</t>
+          <t>Do you have any health concerns or medical conditions that impact your daily life?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>page_2_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>What is your current sleep schedule like?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,127 +635,127 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>page_2_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>Do you take regular exercise or engage in physical activity?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>page_2_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Do you have any financial concerns or debt?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_2_question</t>
+          <t>page_2_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>second_page_question</t>
+          <t>How many people do you live with?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>select_option</t>
+          <t>Do you work from home or have a flexible schedule?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>page_3_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select_option</t>
+          <t>How often do you socialize with friends and family?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>page_3_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Do you have any chronic health conditions that impact your daily life?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What time do you usually wake up and go to bed?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>page_4_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>What is your relationship status?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,40 +814,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>page_4_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Do you have any dependents or family members that rely on you?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>page_4_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Do you have any pets?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,230 +860,230 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form2</t>
+          <t>Do you have any allergies or sensitivities?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_5_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>third_page</t>
+          <t>Do you have any plans for the next few months?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page_3_question</t>
+          <t>page_5_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>third_page_question</t>
+          <t>What is your favorite hobby or activity to do in your free time?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>page_5_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>Do you have any savings or emergency funds?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>How often do you travel or take vacations?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_8</t>
+          <t>page_6_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option</t>
+          <t>Do you have any outstanding loans or debts?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>time_2</t>
+          <t>page_6_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Do you have any plans for retirement or long-term goals?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>page_6_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Do you have any financial concerns?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>page_7_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What is your current financial situation?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,391 +1126,850 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_1_question_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_1_question_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_option_3_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_option_3_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>option_1_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>option_1_choices</t>
+          <t>page_2_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>option_2_choices</t>
+          <t>page_2_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>option_2_choices</t>
+          <t>page_2_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>option_2_choices</t>
+          <t>page_2_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_2_question_choices</t>
+          <t>page_2_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_2_question_choices</t>
+          <t>page_2_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>option_4_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>option_4_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>option_5_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>option_5_choices</t>
+          <t>page_3_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>page_3_question_choices</t>
+          <t>page_3_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>page_3_question_choices</t>
+          <t>page_3_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>option_6_choices</t>
+          <t>page_4_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>option_6_choices</t>
+          <t>page_4_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>option_7_choices</t>
+          <t>page_4_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>married_or_in_a_domestic_partnership</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Married or in a domestic partnership</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>option_7_choices</t>
+          <t>page_4_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>option_8_choices</t>
+          <t>page_4_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>option_8_choices</t>
+          <t>page_4_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>page_4_4_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>page_4_4_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>page_4_4_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>page_5_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>page_5_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>page_5_2_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>page_5_4_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>page_5_4_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>page_5_4_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>page_6_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>page_6_2_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>page_6_2_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>page_6_3_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>page_6_3_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>page_6_3_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>page_6_4_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>page_6_4_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>page_6_4_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>page_7_2_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>page_7_2_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>page_7_2_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
